--- a/DataLake/raw/excel/Raw_Data_Ventas.xlsx
+++ b/DataLake/raw/excel/Raw_Data_Ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Documentos\GitHub\DataLakeSim\DataLake\raw\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A2E8D8-3FD3-456D-B125-0989C58E292A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C576204-B857-4140-AD79-729ABBDD0DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1594,7 +1594,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-25F7-4C6D-AED3-34CCBC104DD4}"/>
+              <c16:uniqueId val="{00000000-6ADE-4F1D-BCF4-3C3231FD07F3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
